--- a/videos/video1/resumen_experimentos.xlsx
+++ b/videos/video1/resumen_experimentos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resultados_Experimentos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Metricas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,10 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,8 +34,15 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,6 +53,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +102,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,94 +487,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:V44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="43" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="61" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Experimento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Modelo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Modo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Variación</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Learning Rate</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Épocas</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Frames</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>NIQE</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>BRISQUE</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>PIQE</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Sigma Ruido</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Nitidez Laplaciana</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Retención Nitidez (%)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Tiempo (min)</t>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Carpeta</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Frames evaluados</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>NIQE media</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>NIQE mediana</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>NIQE desviacion</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>BRISQUE media</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>BRISQUE mediana</t>
+        </is>
+      </c>
+      <c r="K1" s="6" t="inlineStr">
+        <is>
+          <t>BRISQUE desviacion</t>
+        </is>
+      </c>
+      <c r="L1" s="6" t="inlineStr">
+        <is>
+          <t>PIQE media</t>
+        </is>
+      </c>
+      <c r="M1" s="6" t="inlineStr">
+        <is>
+          <t>PIQE mediana</t>
+        </is>
+      </c>
+      <c r="N1" s="6" t="inlineStr">
+        <is>
+          <t>PIQE desviacion</t>
+        </is>
+      </c>
+      <c r="O1" s="6" t="inlineStr">
+        <is>
+          <t>Sigma Ruido media</t>
+        </is>
+      </c>
+      <c r="P1" s="6" t="inlineStr">
+        <is>
+          <t>Sigma Ruido mediana</t>
+        </is>
+      </c>
+      <c r="Q1" s="6" t="inlineStr">
+        <is>
+          <t>Nitidez Laplaciana media</t>
+        </is>
+      </c>
+      <c r="R1" s="6" t="inlineStr">
+        <is>
+          <t>Retencion Nitidez media</t>
+        </is>
+      </c>
+      <c r="S1" s="6" t="inlineStr">
+        <is>
+          <t>Dispositivo</t>
+        </is>
+      </c>
+      <c r="T1" s="6" t="inlineStr">
+        <is>
+          <t>Fecha de ejecucion</t>
+        </is>
+      </c>
+      <c r="U1" s="6" t="inlineStr">
+        <is>
+          <t>Tiempo de ejecucion (min)</t>
+        </is>
+      </c>
+      <c r="V1" s="6" t="inlineStr">
+        <is>
+          <t>Parametros extra</t>
         </is>
       </c>
     </row>
@@ -2833,6 +2912,88 @@
       </c>
       <c r="N43" s="5" t="n">
         <v>1.09</v>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>ensemble_wavelet_triple_sinhud</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Ensemble</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>directo</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>videos/video1/expos/ensemble_wavelet_triple_sinhud</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>6.14629958225353</v>
+      </c>
+      <c r="G44" s="10" t="n">
+        <v>5.7324688592669</v>
+      </c>
+      <c r="H44" s="10" t="n">
+        <v>1.368479309250457</v>
+      </c>
+      <c r="I44" s="10" t="n">
+        <v>45.13444750976562</v>
+      </c>
+      <c r="J44" s="10" t="n">
+        <v>43.22430419921875</v>
+      </c>
+      <c r="K44" s="10" t="n">
+        <v>10.35803073189394</v>
+      </c>
+      <c r="L44" s="10" t="n">
+        <v>71.8857126197815</v>
+      </c>
+      <c r="M44" s="10" t="n">
+        <v>71.42417144775391</v>
+      </c>
+      <c r="N44" s="10" t="n">
+        <v>7.608658013704964</v>
+      </c>
+      <c r="O44" s="10" t="n">
+        <v>2.579688658265382</v>
+      </c>
+      <c r="P44" s="10" t="n">
+        <v>2.965159377316531</v>
+      </c>
+      <c r="Q44" s="10" t="n">
+        <v>67.8858907979744</v>
+      </c>
+      <c r="R44" s="10" t="n">
+        <v>0.6388469235828641</v>
+      </c>
+      <c r="S44" s="9" t="inlineStr">
+        <is>
+          <t>cuda:0</t>
+        </is>
+      </c>
+      <c r="T44" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-10T10:16:47-05:00</t>
+        </is>
+      </c>
+      <c r="U44" s="11" t="n">
+        <v>1.680977422061066</v>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t>Familia=Ensamble, Tipo=Wavelet_Triple, Base=UDVD, Detalles=[StructVert, B2U]</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/videos/video1/resumen_experimentos.xlsx
+++ b/videos/video1/resumen_experimentos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Metricas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experimentos_Activos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,11 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,15 +33,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -53,11 +45,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -87,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -102,24 +89,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -487,154 +456,106 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V44"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="61" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="24" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Experimento</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Modelo</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Modo</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>Carpeta</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>Frames evaluados</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>NIQE media</t>
-        </is>
-      </c>
-      <c r="G1" s="6" t="inlineStr">
-        <is>
-          <t>NIQE mediana</t>
-        </is>
-      </c>
-      <c r="H1" s="6" t="inlineStr">
-        <is>
-          <t>NIQE desviacion</t>
-        </is>
-      </c>
-      <c r="I1" s="6" t="inlineStr">
-        <is>
-          <t>BRISQUE media</t>
-        </is>
-      </c>
-      <c r="J1" s="6" t="inlineStr">
-        <is>
-          <t>BRISQUE mediana</t>
-        </is>
-      </c>
-      <c r="K1" s="6" t="inlineStr">
-        <is>
-          <t>BRISQUE desviacion</t>
-        </is>
-      </c>
-      <c r="L1" s="6" t="inlineStr">
-        <is>
-          <t>PIQE media</t>
-        </is>
-      </c>
-      <c r="M1" s="6" t="inlineStr">
-        <is>
-          <t>PIQE mediana</t>
-        </is>
-      </c>
-      <c r="N1" s="6" t="inlineStr">
-        <is>
-          <t>PIQE desviacion</t>
-        </is>
-      </c>
-      <c r="O1" s="6" t="inlineStr">
-        <is>
-          <t>Sigma Ruido media</t>
-        </is>
-      </c>
-      <c r="P1" s="6" t="inlineStr">
-        <is>
-          <t>Sigma Ruido mediana</t>
-        </is>
-      </c>
-      <c r="Q1" s="6" t="inlineStr">
-        <is>
-          <t>Nitidez Laplaciana media</t>
-        </is>
-      </c>
-      <c r="R1" s="6" t="inlineStr">
-        <is>
-          <t>Retencion Nitidez media</t>
-        </is>
-      </c>
-      <c r="S1" s="6" t="inlineStr">
-        <is>
-          <t>Dispositivo</t>
-        </is>
-      </c>
-      <c r="T1" s="6" t="inlineStr">
-        <is>
-          <t>Fecha de ejecucion</t>
-        </is>
-      </c>
-      <c r="U1" s="6" t="inlineStr">
-        <is>
-          <t>Tiempo de ejecucion (min)</t>
-        </is>
-      </c>
-      <c r="V1" s="6" t="inlineStr">
-        <is>
-          <t>Parametros extra</t>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Variación</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Learning Rate</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Épocas</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Frames</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>NIQE</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BRISQUE</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>PIQE</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Sigma Ruido</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Nitidez Laplaciana</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Retención Nitidez (%)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Tiempo (min)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>n2n_filtromov_orig_1e-4</t>
+          <t>original_video_completo</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Noise2Noise</t>
+          <t>Original</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -644,100 +565,108 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Filtrado Farnebäck</t>
+          <t>Video crudo con telemetría HUD</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>1e-4</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>15</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1000</v>
+        <v>19800</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>7.813</v>
+        <v>5.996</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>66.349</v>
+        <v>47.15</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>81.084</v>
+        <v>59.66</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>1.4337</v>
+        <v>2.506</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>20.71</v>
-      </c>
-      <c r="M2" s="5" t="n">
-        <v>20.31</v>
-      </c>
-      <c r="N2" s="5" t="n">
-        <v>4.34</v>
+        <v>131.47</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>n2n_sinfiltro_orig_1e-4</t>
+          <t>sinhud_video_completo</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Noise2Noise</t>
+          <t>Sin HUD</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>orig</t>
+          <t>sinhud</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Sin filtro de movimiento</t>
+          <t>Pre-procesado con Inpainting ProPainter</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>1e-4</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>15</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1000</v>
+        <v>19800</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>8.191000000000001</v>
+        <v>6.033</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>66.315</v>
+        <v>43.61</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>80.685</v>
+        <v>60.08</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>1.4796</v>
+        <v>3.026</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>8.5</v>
+        <v>137.21</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="N3" s="5" t="n">
-        <v>4.29</v>
+        <v>118.1</v>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>n2n_filtromov_orig_3e-4</t>
+          <t>n2n_orig_completo</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -752,46 +681,48 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Filtrado Farnebäck</t>
+          <t>Filtrado Farnebäck (Video Completo)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>3e-4</t>
+          <t>1e-3</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
         <v>15</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1000</v>
+        <v>19800</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>7.433</v>
+        <v>5.996</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>62.178</v>
+        <v>57.87</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>75.40300000000001</v>
+        <v>75.34</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1.3788</v>
+        <v>1.437</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>49.44</v>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v>40.84</v>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v>4.37</v>
+        <v>74.3</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>n2n_filtromov_orig</t>
+          <t>n2n_sinhud_completo</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -801,12 +732,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>orig</t>
+          <t>sinhud</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Filtrado Farnebäck</t>
+          <t>Filtrado Farnebäck (Video Completo)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -818,88 +749,92 @@
         <v>15</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1000</v>
+        <v>19800</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>7.01</v>
+        <v>5.982</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>57.875</v>
+        <v>54.08</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>75.34</v>
+        <v>81.3</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1.4366</v>
+        <v>2.271</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>74.3</v>
+        <v>44.38</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>57.98</v>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v>2.21</v>
+        <v>43.7</v>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>n2n_filtromov_sinhud_3e-4</t>
+          <t>n2v_orig_completo</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Noise2Noise</t>
+          <t>Noise2Void</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>sinhud</t>
+          <t>orig</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Filtrado Farnebäck</t>
+          <t>N2V2 Blur-Pool (Video Completo)</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>3e-4</t>
+          <t>1e-3</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
         <v>15</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1000</v>
+        <v>19800</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>7.73</v>
+        <v>6.638</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>54.97</v>
+        <v>58.5</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>80.98099999999999</v>
+        <v>72.73</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2.2061</v>
+        <v>1.735</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>19.48</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v>2.7</v>
+        <v>76.93000000000001</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>n2v_clasico_orig_lr1e4</t>
+          <t>n2v_sinhud_completo</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -909,56 +844,58 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>orig</t>
+          <t>sinhud</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>N2V Clásico Krull 2019</t>
+          <t>N2V2 Blur-Pool (Video Completo)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>1e-4</t>
+          <t>1e-3</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
         <v>15</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1000</v>
+        <v>19800</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.038</v>
+        <v>7.045</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>67.559</v>
+        <v>53.59</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>80.48999999999999</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1.4025</v>
+        <v>2.233</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>19.95</v>
+        <v>41.46</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>19.31</v>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v>4.25</v>
+        <v>42.6</v>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>n2v2_orig_1e-4</t>
+          <t>n2n_sinfiltro_orig</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>N2V2</t>
+          <t>Noise2Noise</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -968,7 +905,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Noise2Void con Blur-Pool y pixel ciego</t>
+          <t>Sin filtro de movimiento</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -983,36 +920,36 @@
         <v>1000</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>7.912</v>
+        <v>8.191000000000001</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>65.914</v>
+        <v>66.315</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>80.893</v>
+        <v>80.685</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.3699</v>
+        <v>1.4796</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>16.46</v>
+        <v>8.5</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>15.68</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>4.23</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>n2v2_orig_3e-4</t>
+          <t>n2n_filtromov_orig_3e-4</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>N2V2</t>
+          <t>Noise2Noise</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1022,7 +959,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Noise2Void con Blur-Pool y pixel ciego</t>
+          <t>Filtrado Farnebäck</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1037,36 +974,36 @@
         <v>1000</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>7.443</v>
+        <v>7.433</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>60.072</v>
+        <v>62.178</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>77.46899999999999</v>
+        <v>75.40300000000001</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.3832</v>
+        <v>1.3788</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>40.78</v>
+        <v>49.44</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>36.8</v>
+        <v>40.84</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>4.25</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>n2v2_orig</t>
+          <t>n2n_filtromov_orig</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>N2V2</t>
+          <t>Noise2Noise</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1076,7 +1013,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Noise2Void con Blur-Pool y pixel ciego</t>
+          <t>Filtrado Farnebäck</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1091,46 +1028,46 @@
         <v>1000</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>6.911</v>
+        <v>7.01</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>58.503</v>
+        <v>57.875</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>72.726</v>
+        <v>75.34</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.7346</v>
+        <v>1.4366</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>76.93000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>64.55</v>
+        <v>57.98</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>4.29</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>struct_n2v_horiz_orig_3e-4</t>
+          <t>n2n_filtromov_sinhud_3e-4</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>StructN2V</t>
+          <t>Noise2Noise</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>orig</t>
+          <t>sinhud</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Máscara ciega lineal Horizontal 5px</t>
+          <t>Filtrado Farnebäck</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1145,51 +1082,51 @@
         <v>1000</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>7.824</v>
+        <v>7.73</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>62.676</v>
+        <v>54.97</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>78.76900000000001</v>
+        <v>80.98099999999999</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.3655</v>
+        <v>2.2061</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v>30.18</v>
+        <v>19.48</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>4.22</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>n2v2_sinhud_3e-4</t>
+          <t>n2v_clasico_orig_lr1e4</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>N2V2</t>
+          <t>Noise2Void</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>sinhud</t>
+          <t>orig</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Noise2Void con Blur-Pool y pixel ciego</t>
+          <t>N2V Clásico Krull 2019</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>3e-4</t>
+          <t>1e-4</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
@@ -1199,36 +1136,36 @@
         <v>1000</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>7.327</v>
+        <v>8.038</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>53.587</v>
+        <v>67.559</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>81.848</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.2328</v>
+        <v>1.4025</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>41.46</v>
+        <v>19.95</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>42.61</v>
+        <v>19.31</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>2.7</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>neighbor2neighbor_orig_3e-4</t>
+          <t>n2v2_orig_3e-4</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Neighbor2Neighbor</t>
+          <t>N2V2</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1238,7 +1175,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Submuestreo de celdas 2x2 con regularizador</t>
+          <t>Noise2Void con Blur-Pool y pixel ciego</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1253,36 +1190,36 @@
         <v>1000</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>7.299</v>
+        <v>7.443</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>58.177</v>
+        <v>60.072</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>76.71899999999999</v>
+        <v>77.46899999999999</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.45</v>
+        <v>1.3832</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>32.29</v>
+        <v>40.78</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>26.82</v>
+        <v>36.8</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>blind2unblind_orig_3e-4</t>
+          <t>n2v2_orig</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Blind2Unblind</t>
+          <t>N2V2</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1292,12 +1229,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Máscara de Visibilidad Estructurada</t>
+          <t>Noise2Void con Blur-Pool y pixel ciego</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>3e-4</t>
+          <t>1e-3</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
@@ -1307,51 +1244,51 @@
         <v>1000</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>7.165</v>
+        <v>6.911</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>58.195</v>
+        <v>58.503</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>75.34</v>
+        <v>72.726</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.4292</v>
+        <v>1.7346</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>46.78</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>39.69</v>
+        <v>64.55</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>4.34</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>n2n_filtromov_sinhud</t>
+          <t>struct_n2v_horiz_orig_3e-4</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Noise2Noise</t>
+          <t>StructN2V</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>sinhud</t>
+          <t>orig</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Filtrado Farnebäck</t>
+          <t>Máscara ciega lineal Horizontal 5px</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>1e-3</t>
+          <t>3e-4</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
@@ -1361,36 +1298,36 @@
         <v>1000</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>6.968</v>
+        <v>7.824</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>54.077</v>
+        <v>62.676</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>81.303</v>
+        <v>78.76900000000001</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.2713</v>
+        <v>1.3655</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>44.38</v>
+        <v>34.1</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>43.72</v>
+        <v>30.18</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>1.48</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>struct_n2v_horiz_sinhud</t>
+          <t>n2v2_sinhud_3e-4</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>StructN2V</t>
+          <t>N2V2</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1400,12 +1337,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Máscara ciega lineal Horizontal 5px</t>
+          <t>Noise2Void con Blur-Pool y pixel ciego</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>1e-3</t>
+          <t>3e-4</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
@@ -1415,36 +1352,36 @@
         <v>1000</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>6.81</v>
+        <v>7.327</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>51.393</v>
+        <v>53.587</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>78.123</v>
+        <v>81.848</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.5308</v>
+        <v>2.2328</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>54.15</v>
+        <v>41.46</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>54.6</v>
+        <v>42.61</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>1.32</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>struct_n2v_horiz_orig</t>
+          <t>neighbor2neighbor_orig_3e-4</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>StructN2V</t>
+          <t>Neighbor2Neighbor</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1454,12 +1391,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Máscara ciega lineal Horizontal 5px</t>
+          <t>Submuestreo de celdas 2x2 con regularizador</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>1e-3</t>
+          <t>3e-4</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
@@ -1469,51 +1406,51 @@
         <v>1000</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>7.36</v>
+        <v>7.299</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>55.415</v>
+        <v>58.177</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>74.05200000000001</v>
+        <v>76.71899999999999</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.5819</v>
+        <v>1.45</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>57.49</v>
+        <v>32.29</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>47.62</v>
+        <v>26.82</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>2.17</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>struct_n2v_vert_sinhud</t>
+          <t>blind2unblind_orig_3e-4</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>StructN2V</t>
+          <t>Blind2Unblind</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>sinhud</t>
+          <t>orig</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Máscara ciega lineal Vertical 5px (Supresión FPN)</t>
+          <t>Máscara de Visibilidad Estructurada</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>1e-3</t>
+          <t>3e-4</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
@@ -1523,46 +1460,46 @@
         <v>1000</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>6.503</v>
+        <v>7.165</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>50.7</v>
+        <v>58.195</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>75.848</v>
+        <v>75.34</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.6256</v>
+        <v>1.4292</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>92.29000000000001</v>
+        <v>46.78</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>88.42</v>
+        <v>39.69</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>1.3</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>struct_n2v_vert_orig</t>
+          <t>n2n_filtromov_sinhud</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>StructN2V</t>
+          <t>Noise2Noise</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>orig</t>
+          <t>sinhud</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Máscara ciega lineal Vertical 5px (Supresión FPN)</t>
+          <t>Filtrado Farnebäck</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1577,31 +1514,31 @@
         <v>1000</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>6.84</v>
+        <v>6.968</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>55.715</v>
+        <v>54.077</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>71.863</v>
+        <v>81.303</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.8162</v>
+        <v>2.2713</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>101.28</v>
+        <v>44.38</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>84.09</v>
+        <v>43.72</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>2.33</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>struct_n2v_cross_sinhud</t>
+          <t>struct_n2v_horiz_sinhud</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1616,7 +1553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Máscara ciega en Cruz 5px</t>
+          <t>Máscara ciega lineal Horizontal 5px</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1631,31 +1568,31 @@
         <v>1000</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>7.239</v>
+        <v>6.81</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>58.146</v>
+        <v>51.393</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>80.21299999999999</v>
+        <v>78.123</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.3277</v>
+        <v>2.5308</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>35.83</v>
+        <v>54.15</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>35.78</v>
+        <v>54.6</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>struct_n2v_cross_orig</t>
+          <t>struct_n2v_horiz_orig</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1670,7 +1607,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Máscara ciega en Cruz 5px</t>
+          <t>Máscara ciega lineal Horizontal 5px</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1685,36 +1622,36 @@
         <v>1000</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>7.485</v>
+        <v>7.36</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>62.581</v>
+        <v>55.415</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>73.41200000000001</v>
+        <v>74.05200000000001</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.5226</v>
+        <v>1.5819</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>48.2</v>
+        <v>57.49</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>43.16</v>
+        <v>47.62</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>blind2unblind_sinhud</t>
+          <t>struct_n2v_vert_sinhud</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Blind2Unblind</t>
+          <t>StructN2V</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1724,7 +1661,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Máscara de Visibilidad Estructurada</t>
+          <t>Máscara ciega lineal Vertical 5px (Supresión FPN)</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1739,36 +1676,36 @@
         <v>1000</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>6.409</v>
+        <v>6.503</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>45.344</v>
+        <v>50.7</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>71.669</v>
+        <v>75.848</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.7457</v>
+        <v>2.6256</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>80.84</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>76.42</v>
+        <v>88.42</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>blind2unblind_orig</t>
+          <t>struct_n2v_vert_orig</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Blind2Unblind</t>
+          <t>StructN2V</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1778,7 +1715,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Máscara de Visibilidad Estructurada</t>
+          <t>Máscara ciega lineal Vertical 5px (Supresión FPN)</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1793,36 +1730,36 @@
         <v>1000</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>6.702</v>
+        <v>6.84</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>54.314</v>
+        <v>55.715</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>74.63</v>
+        <v>71.863</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.5122</v>
+        <v>1.8162</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>82.43000000000001</v>
+        <v>101.28</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>64.95999999999999</v>
+        <v>84.09</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>neighbor2neighbor_sinhud</t>
+          <t>struct_n2v_cross_sinhud</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Neighbor2Neighbor</t>
+          <t>StructN2V</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1832,7 +1769,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Submuestreo de celdas 2x2 con regularizador</t>
+          <t>Máscara ciega en Cruz 5px</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1847,36 +1784,36 @@
         <v>1000</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>6.494</v>
+        <v>7.239</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>47.015</v>
+        <v>58.146</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>67.37</v>
+        <v>80.21299999999999</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.937</v>
+        <v>2.3277</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>90.48999999999999</v>
+        <v>35.83</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>82.28</v>
+        <v>35.78</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>neighbor2neighbor_orig</t>
+          <t>struct_n2v_cross_orig</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Neighbor2Neighbor</t>
+          <t>StructN2V</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1886,7 +1823,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Submuestreo de celdas 2x2 con regularizador</t>
+          <t>Máscara ciega en Cruz 5px</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1901,36 +1838,36 @@
         <v>1000</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>6.669</v>
+        <v>7.485</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>55.52</v>
+        <v>62.581</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>73.27200000000001</v>
+        <v>73.41200000000001</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.7198</v>
+        <v>1.5226</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>89.08</v>
+        <v>48.2</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>68.63</v>
+        <v>43.16</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>frames2residual_sinhud</t>
+          <t>blind2unblind_sinhud</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Frames2Residual</t>
+          <t>Blind2Unblind</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1940,7 +1877,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Resta Residual Ingenua (T=5)</t>
+          <t>Máscara de Visibilidad Estructurada</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1955,36 +1892,36 @@
         <v>1000</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>24.325</v>
+        <v>6.409</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>125.265</v>
+        <v>45.344</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>98.07599999999999</v>
+        <v>71.669</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>239.9718</v>
+        <v>2.7457</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>84864.92999999999</v>
+        <v>80.84</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>92321.39</v>
+        <v>76.42</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>frames2residual_orig</t>
+          <t>blind2unblind_orig</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Frames2Residual</t>
+          <t>Blind2Unblind</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1994,7 +1931,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Resta Residual Ingenua (T=5)</t>
+          <t>Máscara de Visibilidad Estructurada</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -2009,36 +1946,36 @@
         <v>1000</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>611.423</v>
+        <v>6.702</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>153.591</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>100</v>
+        <v>54.314</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>74.63</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>222.387</v>
+        <v>1.5122</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>95470.63</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>105392.84</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>fastdvdnet_sinhud</t>
+          <t>neighbor2neighbor_sinhud</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>FastDVDnet</t>
+          <t>Neighbor2Neighbor</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -2048,7 +1985,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Doble U-Net en Cascada (T=5)</t>
+          <t>Submuestreo de celdas 2x2 con regularizador</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -2063,36 +2000,36 @@
         <v>1000</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>7.103</v>
+        <v>6.494</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>52.362</v>
+        <v>47.015</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>79.23699999999999</v>
+        <v>67.37</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.1216</v>
+        <v>2.937</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>20.27</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>18.4</v>
+        <v>82.28</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>fastdvdnet_orig</t>
+          <t>neighbor2neighbor_orig</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>FastDVDnet</t>
+          <t>Neighbor2Neighbor</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2102,7 +2039,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Doble U-Net en Cascada (T=5)</t>
+          <t>Submuestreo de celdas 2x2 con regularizador</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -2117,36 +2054,36 @@
         <v>1000</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7.311</v>
+        <v>6.669</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>60.438</v>
+        <v>55.52</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>75.553</v>
+        <v>73.27200000000001</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.4248</v>
+        <v>1.7198</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>56.71</v>
+        <v>89.08</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>47.07</v>
+        <v>68.63</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>2.16</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>rvidenet_sinhud</t>
+          <t>frames2residual_sinhud</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>RViDeNet</t>
+          <t>Frames2Residual</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2156,7 +2093,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Memoria Recurrente ConvGRU</t>
+          <t>Resta Residual Ingenua (T=5)</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2170,37 +2107,37 @@
       <c r="G30" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="H30" s="3" t="n">
-        <v>7</v>
+      <c r="H30" s="4" t="n">
+        <v>24.325</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>47.842</v>
+        <v>125.265</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>72.711</v>
+        <v>98.07599999999999</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2.7872</v>
+        <v>239.9718</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>27.72</v>
+        <v>84864.92999999999</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>26.83</v>
+        <v>92321.39</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>rvidenet_orig</t>
+          <t>frames2residual_orig</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>RViDeNet</t>
+          <t>Frames2Residual</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2210,7 +2147,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Memoria Recurrente ConvGRU</t>
+          <t>Resta Residual Ingenua (T=5)</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2225,36 +2162,36 @@
         <v>1000</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>6.992</v>
+        <v>611.423</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>54.931</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>64.31</v>
+        <v>153.591</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>100</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.5337</v>
+        <v>222.387</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>71.89</v>
+        <v>95470.63</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>57.83</v>
+        <v>105392.84</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>2.29</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>udvd_sinhud</t>
+          <t>fastdvdnet_sinhud</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>UDVD</t>
+          <t>FastDVDnet</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -2264,7 +2201,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Kernels Dinámicos Adaptativos 5x5 (T=5)</t>
+          <t>Doble U-Net en Cascada (T=5)</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2279,36 +2216,36 @@
         <v>1000</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.198</v>
+        <v>7.103</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>45.689</v>
+        <v>52.362</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>64.81999999999999</v>
+        <v>79.23699999999999</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2.5604</v>
+        <v>2.1216</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>110.33</v>
+        <v>20.27</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>92.26000000000001</v>
+        <v>18.4</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>udvd_orig</t>
+          <t>fastdvdnet_orig</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>UDVD</t>
+          <t>FastDVDnet</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2318,7 +2255,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Kernels Dinámicos Adaptativos 5x5 (T=5)</t>
+          <t>Doble U-Net en Cascada (T=5)</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2333,36 +2270,36 @@
         <v>1000</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.519</v>
+        <v>7.311</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>54.17</v>
+        <v>60.438</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>65.76300000000001</v>
+        <v>75.553</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.1735</v>
+        <v>1.4248</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>112.34</v>
+        <v>56.71</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>83.72</v>
+        <v>47.07</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>bilateral_temporal_sinhud</t>
+          <t>rvidenet_sinhud</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Bilateral 3D</t>
+          <t>RViDeNet</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -2372,53 +2309,51 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Filtro Bilateral Espacio-Temporal 3D (d=7, T=5)</t>
+          <t>Memoria Recurrente ConvGRU</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>1e-3</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="H34" s="4" t="n">
-        <v>7.376</v>
+      <c r="H34" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>56.927</v>
+        <v>47.842</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>78.328</v>
+        <v>72.711</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1.7346</v>
+        <v>2.7872</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>110.66</v>
+        <v>27.72</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>92.94</v>
+        <v>26.83</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>bilateral_temporal_orig</t>
+          <t>rvidenet_orig</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Bilateral 3D</t>
+          <t>RViDeNet</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -2428,53 +2363,51 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Filtro Bilateral Espacio-Temporal 3D (d=7, T=5)</t>
+          <t>Memoria Recurrente ConvGRU</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>1e-3</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>1000</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>7.674</v>
+        <v>6.992</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>69.43600000000001</v>
+        <v>54.931</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>74.45699999999999</v>
+        <v>64.31</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1.4114</v>
+        <v>2.5337</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>109.95</v>
+        <v>71.89</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>82.04000000000001</v>
+        <v>57.83</v>
       </c>
       <c r="N35" s="5" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>ensemble_wavelet_f2r_b2u_sinhud</t>
+          <t>udvd_sinhud</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Ensemble Wavelet</t>
+          <t>UDVD</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -2484,7 +2417,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Fusión preliminar Fase 1 (Frames2Residual + Blind2Unblind)</t>
+          <t>Kernels Dinámicos Adaptativos 5x5 (T=5)</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -2492,45 +2425,43 @@
           <t>1e-3</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F36" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>1000</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>4.732</v>
+        <v>6.198</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>27.416</v>
+        <v>45.689</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>42.933</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>4.2965</v>
+        <v>2.5604</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>65.98</v>
+        <v>110.33</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>64.31999999999999</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>ensemble_wavelet_f2r_b2u_orig</t>
+          <t>udvd_orig</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Ensemble Wavelet</t>
+          <t>UDVD</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2540,7 +2471,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Fusión preliminar Fase 1 (Frames2Residual + Blind2Unblind)</t>
+          <t>Kernels Dinámicos Adaptativos 5x5 (T=5)</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -2548,45 +2479,43 @@
           <t>1e-3</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F37" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>1000</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>6.432</v>
+        <v>6.519</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>22.968</v>
+        <v>54.17</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>12.632</v>
+        <v>65.76300000000001</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>3.321</v>
+        <v>2.1735</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>58.8</v>
+        <v>112.34</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>48.54</v>
+        <v>83.72</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ensemble_promedio_fase1_sinhud</t>
+          <t>bilateral_temporal_sinhud</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Ensemble Promedio</t>
+          <t>Bilateral 3D</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -2596,12 +2525,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Promedio ponderado preliminar Fase 1</t>
+          <t>Filtro Bilateral Espacio-Temporal 3D (d=7, T=5)</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>1e-3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -2613,36 +2542,36 @@
         <v>1000</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>6.985</v>
+        <v>7.376</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>52.199</v>
+        <v>56.927</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>79.17</v>
+        <v>78.328</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>2.3039</v>
+        <v>1.7346</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>26.87</v>
+        <v>110.66</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>25.96</v>
+        <v>92.94</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>ensemble_promedio_fase1_orig</t>
+          <t>bilateral_temporal_orig</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Ensemble Promedio</t>
+          <t>Bilateral 3D</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2652,12 +2581,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Promedio ponderado preliminar Fase 1</t>
+          <t>Filtro Bilateral Espacio-Temporal 3D (d=7, T=5)</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>1e-3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -2669,31 +2598,31 @@
         <v>1000</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>7.241</v>
+        <v>7.674</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>60.491</v>
+        <v>69.43600000000001</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>75.971</v>
+        <v>74.45699999999999</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>1.401</v>
+        <v>1.4114</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>46.48</v>
+        <v>109.95</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>38.61</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ensemble_wavelet_udvd_struct_vert_sinhud</t>
+          <t>ensemble_wavelet_f2r_b2u_sinhud</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2703,12 +2632,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>orig</t>
+          <t>sinhud</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Base Temporal UDVD + Detalle Desrayado StructN2V Vert</t>
+          <t>Fusión preliminar Fase 1 (Frames2Residual + Blind2Unblind)</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -2725,31 +2654,31 @@
         <v>1000</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>6.13</v>
+        <v>4.732</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>45.78</v>
+        <v>27.416</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>70.47499999999999</v>
+        <v>42.933</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>2.7087</v>
+        <v>4.2965</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>87.45999999999999</v>
+        <v>65.98</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>82.92</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>1.81</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ensemble_wavelet_udvd_b2u_sinhud</t>
+          <t>ensemble_wavelet_f2r_b2u_orig</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2764,7 +2693,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Base Temporal UDVD + Detalle Perceptual Blind2Unblind</t>
+          <t>Fusión preliminar Fase 1 (Frames2Residual + Blind2Unblind)</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2781,46 +2710,46 @@
         <v>1000</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>6.052</v>
+        <v>6.432</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>40.623</v>
+        <v>22.968</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>64.809</v>
+        <v>12.632</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>2.7828</v>
+        <v>3.321</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>77.22</v>
+        <v>58.8</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>71.81999999999999</v>
+        <v>48.54</v>
       </c>
       <c r="N41" s="5" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ensemble_ponderado_top3_sinhud</t>
+          <t>ensemble_promedio_fastdvd_struct_cross_b2u_sinhud</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Ensemble Ponderado</t>
+          <t>Ensemble Promedio</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>orig</t>
+          <t>sinhud</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>UDVD (0.45) + StructN2V Vert (0.35) + Blind2Unblind (0.20)</t>
+          <t>Promedio ponderado preliminar Fase 1</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2837,163 +2766,305 @@
         <v>1000</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>6.169</v>
+        <v>6.985</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>48.607</v>
+        <v>52.199</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>74.429</v>
+        <v>79.17</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>2.507</v>
+        <v>2.3039</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>76.70999999999999</v>
+        <v>26.87</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>70.29000000000001</v>
+        <v>25.96</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ensemble_mediana_top3_sinhud</t>
+          <t>ensemble_promedio_fastdvd_struct_cross_b2u_orig</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
+          <t>Ensemble Promedio</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>orig</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Promedio ponderado preliminar Fase 1</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>1e-3</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>7.241</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>60.491</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>75.971</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>1.401</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="N43" s="5" t="n">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>ensemble_wavelet_udvd_struct_vert_sinhud</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Ensemble Wavelet</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>orig</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Base Temporal UDVD + Detalle Desrayado StructN2V Vert</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>1e-3</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>70.47499999999999</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>2.7087</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>87.45999999999999</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>82.92</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>ensemble_wavelet_udvd_b2u_sinhud</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Ensemble Wavelet</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>orig</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Base Temporal UDVD + Detalle Perceptual Blind2Unblind</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>1e-3</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>6.052</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>40.623</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>64.809</v>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>2.7828</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>77.22</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>71.81999999999999</v>
+      </c>
+      <c r="N45" s="5" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>ensemble_ponderado_udvd_struct_vert_b2u_sinhud</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Ensemble Ponderado</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>orig</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>UDVD (0.45) + StructN2V Vert (0.35) + Blind2Unblind (0.20)</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>1e-3</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>6.169</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>48.607</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>74.429</v>
+      </c>
+      <c r="K46" s="4" t="n">
+        <v>2.507</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>76.70999999999999</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>70.29000000000001</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>ensemble_mediana_udvd_struct_vert_b2u_sinhud</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>Ensemble Mediana</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>orig</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Mediana no-lineal de UDVD + StructN2V Vert + Blind2Unblind</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>1e-3</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>1e-3</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G43" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H43" s="4" t="n">
+      <c r="G47" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H47" s="4" t="n">
         <v>6.782</v>
       </c>
-      <c r="I43" s="4" t="n">
+      <c r="I47" s="4" t="n">
         <v>49.022</v>
       </c>
-      <c r="J43" s="4" t="n">
+      <c r="J47" s="4" t="n">
         <v>74.423</v>
       </c>
-      <c r="K43" s="4" t="n">
+      <c r="K47" s="4" t="n">
         <v>2.6271</v>
       </c>
-      <c r="L43" s="5" t="n">
+      <c r="L47" s="5" t="n">
         <v>80.66</v>
       </c>
-      <c r="M43" s="5" t="n">
+      <c r="M47" s="5" t="n">
         <v>73.81999999999999</v>
       </c>
-      <c r="N43" s="5" t="n">
+      <c r="N47" s="5" t="n">
         <v>1.09</v>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>ensemble_wavelet_triple_sinhud</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Ensemble</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t>directo</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>videos/video1/expos/ensemble_wavelet_triple_sinhud</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F44" s="10" t="n">
-        <v>6.14629958225353</v>
-      </c>
-      <c r="G44" s="10" t="n">
-        <v>5.7324688592669</v>
-      </c>
-      <c r="H44" s="10" t="n">
-        <v>1.368479309250457</v>
-      </c>
-      <c r="I44" s="10" t="n">
-        <v>45.13444750976562</v>
-      </c>
-      <c r="J44" s="10" t="n">
-        <v>43.22430419921875</v>
-      </c>
-      <c r="K44" s="10" t="n">
-        <v>10.35803073189394</v>
-      </c>
-      <c r="L44" s="10" t="n">
-        <v>71.8857126197815</v>
-      </c>
-      <c r="M44" s="10" t="n">
-        <v>71.42417144775391</v>
-      </c>
-      <c r="N44" s="10" t="n">
-        <v>7.608658013704964</v>
-      </c>
-      <c r="O44" s="10" t="n">
-        <v>2.579688658265382</v>
-      </c>
-      <c r="P44" s="10" t="n">
-        <v>2.965159377316531</v>
-      </c>
-      <c r="Q44" s="10" t="n">
-        <v>67.8858907979744</v>
-      </c>
-      <c r="R44" s="10" t="n">
-        <v>0.6388469235828641</v>
-      </c>
-      <c r="S44" s="9" t="inlineStr">
-        <is>
-          <t>cuda:0</t>
-        </is>
-      </c>
-      <c r="T44" s="9" t="inlineStr">
-        <is>
-          <t>2026-09-10T10:16:47-05:00</t>
-        </is>
-      </c>
-      <c r="U44" s="11" t="n">
-        <v>1.680977422061066</v>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t>Familia=Ensamble, Tipo=Wavelet_Triple, Base=UDVD, Detalles=[StructVert, B2U]</t>
-        </is>
       </c>
     </row>
   </sheetData>
